--- a/research/traditional_assets/database/data/pakistan/pakistan_r_e_i_t.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_r_e_i_t.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0355</v>
+        <v>0.0475</v>
       </c>
       <c r="E2">
-        <v>-0.133</v>
+        <v>0.209</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,34 +600,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.8385416666666667</v>
+        <v>0.8279569892473118</v>
       </c>
       <c r="J2">
-        <v>0.8385416666666667</v>
+        <v>0.8279569892473118</v>
       </c>
       <c r="K2">
-        <v>51.4</v>
+        <v>47.8</v>
       </c>
       <c r="L2">
-        <v>2.677083333333333</v>
+        <v>2.569892473118279</v>
       </c>
       <c r="M2">
-        <v>16.2</v>
+        <v>15.4</v>
       </c>
       <c r="N2">
-        <v>0.1056751467710372</v>
+        <v>0.1149253731343284</v>
       </c>
       <c r="O2">
-        <v>0.3151750972762646</v>
+        <v>0.3221757322175732</v>
       </c>
       <c r="P2">
-        <v>16.2</v>
+        <v>15.4</v>
       </c>
       <c r="Q2">
-        <v>0.1056751467710372</v>
+        <v>0.1149253731343284</v>
       </c>
       <c r="R2">
-        <v>0.3151750972762646</v>
+        <v>0.3221757322175732</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,31 +636,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.8</v>
+        <v>4.65</v>
       </c>
       <c r="V2">
-        <v>0.01174168297455969</v>
+        <v>0.03470149253731344</v>
       </c>
       <c r="W2">
-        <v>0.1658064516129032</v>
+        <v>0.1315354980737479</v>
       </c>
       <c r="X2">
-        <v>0.09513378766835336</v>
+        <v>0.1354779798136211</v>
       </c>
       <c r="Y2">
-        <v>0.07067266394454987</v>
+        <v>-0.003942481739873216</v>
       </c>
       <c r="Z2">
-        <v>0.06339981508387267</v>
+        <v>0.05184668989547039</v>
       </c>
       <c r="AA2">
-        <v>0.05316338660678907</v>
+        <v>0.04292682926829269</v>
       </c>
       <c r="AB2">
-        <v>0.09513378766835336</v>
+        <v>0.1354779798136211</v>
       </c>
       <c r="AC2">
-        <v>-0.04197040106156429</v>
+        <v>-0.09255115054532845</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-1.8</v>
+        <v>-4.65</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -681,19 +681,19 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.01188118811881188</v>
+        <v>-0.03594897564746811</v>
       </c>
       <c r="AK2">
-        <v>-0.00537795040334628</v>
+        <v>-0.01506072874493927</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.53</v>
+        <v>-0.62</v>
       </c>
       <c r="AQ2">
-        <v>-30.37735849056604</v>
+        <v>-24.83870967741936</v>
       </c>
     </row>
     <row r="3">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0355</v>
+        <v>0.0475</v>
       </c>
       <c r="E3">
-        <v>-0.133</v>
+        <v>0.209</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -725,34 +725,34 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.8385416666666667</v>
+        <v>0.8279569892473118</v>
       </c>
       <c r="J3">
-        <v>0.8385416666666667</v>
+        <v>0.8279569892473118</v>
       </c>
       <c r="K3">
-        <v>51.4</v>
+        <v>47.8</v>
       </c>
       <c r="L3">
-        <v>2.677083333333333</v>
+        <v>2.569892473118279</v>
       </c>
       <c r="M3">
-        <v>16.2</v>
+        <v>15.4</v>
       </c>
       <c r="N3">
-        <v>0.1056751467710372</v>
+        <v>0.1149253731343284</v>
       </c>
       <c r="O3">
-        <v>0.3151750972762646</v>
+        <v>0.3221757322175732</v>
       </c>
       <c r="P3">
-        <v>16.2</v>
+        <v>15.4</v>
       </c>
       <c r="Q3">
-        <v>0.1056751467710372</v>
+        <v>0.1149253731343284</v>
       </c>
       <c r="R3">
-        <v>0.3151750972762646</v>
+        <v>0.3221757322175732</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -761,31 +761,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.8</v>
+        <v>4.65</v>
       </c>
       <c r="V3">
-        <v>0.01174168297455969</v>
+        <v>0.03470149253731344</v>
       </c>
       <c r="W3">
-        <v>0.1658064516129032</v>
+        <v>0.1315354980737479</v>
       </c>
       <c r="X3">
-        <v>0.09513378766835336</v>
+        <v>0.1354779798136211</v>
       </c>
       <c r="Y3">
-        <v>0.07067266394454987</v>
+        <v>-0.003942481739873216</v>
       </c>
       <c r="Z3">
-        <v>0.06339981508387267</v>
+        <v>0.05184668989547039</v>
       </c>
       <c r="AA3">
-        <v>0.05316338660678907</v>
+        <v>0.04292682926829269</v>
       </c>
       <c r="AB3">
-        <v>0.09513378766835336</v>
+        <v>0.1354779798136211</v>
       </c>
       <c r="AC3">
-        <v>-0.04197040106156429</v>
+        <v>-0.09255115054532845</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -797,7 +797,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-1.8</v>
+        <v>-4.65</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -806,19 +806,19 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.01188118811881188</v>
+        <v>-0.03594897564746811</v>
       </c>
       <c r="AK3">
-        <v>-0.00537795040334628</v>
+        <v>-0.01506072874493927</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.53</v>
+        <v>-0.62</v>
       </c>
       <c r="AQ3">
-        <v>-30.37735849056604</v>
+        <v>-24.83870967741936</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/pakistan/pakistan_r_e_i_t.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_r_e_i_t.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0475</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="E2">
-        <v>0.209</v>
+        <v>0.132</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,34 +600,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.8279569892473118</v>
+        <v>0.8363636363636364</v>
       </c>
       <c r="J2">
-        <v>0.8279569892473118</v>
+        <v>0.8363636363636364</v>
       </c>
       <c r="K2">
-        <v>47.8</v>
+        <v>32.9</v>
       </c>
       <c r="L2">
-        <v>2.569892473118279</v>
+        <v>1.993939393939394</v>
       </c>
       <c r="M2">
-        <v>15.4</v>
+        <v>14.1</v>
       </c>
       <c r="N2">
-        <v>0.1149253731343284</v>
+        <v>0.1287671232876712</v>
       </c>
       <c r="O2">
-        <v>0.3221757322175732</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="P2">
-        <v>15.4</v>
+        <v>14.1</v>
       </c>
       <c r="Q2">
-        <v>0.1149253731343284</v>
+        <v>0.1287671232876712</v>
       </c>
       <c r="R2">
-        <v>0.3221757322175732</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,31 +636,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>4.65</v>
+        <v>3.81</v>
       </c>
       <c r="V2">
-        <v>0.03470149253731344</v>
+        <v>0.03479452054794521</v>
       </c>
       <c r="W2">
-        <v>0.1315354980737479</v>
+        <v>0.1172905525846702</v>
       </c>
       <c r="X2">
-        <v>0.1354779798136211</v>
+        <v>0.1352668946829672</v>
       </c>
       <c r="Y2">
-        <v>-0.003942481739873216</v>
+        <v>-0.01797634209829699</v>
       </c>
       <c r="Z2">
-        <v>0.05184668989547039</v>
+        <v>0.05964214711729623</v>
       </c>
       <c r="AA2">
-        <v>0.04292682926829269</v>
+        <v>0.04988252304355685</v>
       </c>
       <c r="AB2">
-        <v>0.1354779798136211</v>
+        <v>0.1352668946829672</v>
       </c>
       <c r="AC2">
-        <v>-0.09255115054532845</v>
+        <v>-0.08538437163941036</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-4.65</v>
+        <v>-3.81</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -681,19 +681,19 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.03594897564746811</v>
+        <v>-0.0360488220266818</v>
       </c>
       <c r="AK2">
-        <v>-0.01506072874493927</v>
+        <v>-0.01602254089743051</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.62</v>
+        <v>-0.97</v>
       </c>
       <c r="AQ2">
-        <v>-24.83870967741936</v>
+        <v>-14.22680412371134</v>
       </c>
     </row>
     <row r="3">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0475</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="E3">
-        <v>0.209</v>
+        <v>0.132</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -725,34 +725,34 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.8279569892473118</v>
+        <v>0.8363636363636364</v>
       </c>
       <c r="J3">
-        <v>0.8279569892473118</v>
+        <v>0.8363636363636364</v>
       </c>
       <c r="K3">
-        <v>47.8</v>
+        <v>32.9</v>
       </c>
       <c r="L3">
-        <v>2.569892473118279</v>
+        <v>1.993939393939394</v>
       </c>
       <c r="M3">
-        <v>15.4</v>
+        <v>14.1</v>
       </c>
       <c r="N3">
-        <v>0.1149253731343284</v>
+        <v>0.1287671232876712</v>
       </c>
       <c r="O3">
-        <v>0.3221757322175732</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="P3">
-        <v>15.4</v>
+        <v>14.1</v>
       </c>
       <c r="Q3">
-        <v>0.1149253731343284</v>
+        <v>0.1287671232876712</v>
       </c>
       <c r="R3">
-        <v>0.3221757322175732</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -761,31 +761,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>4.65</v>
+        <v>3.81</v>
       </c>
       <c r="V3">
-        <v>0.03470149253731344</v>
+        <v>0.03479452054794521</v>
       </c>
       <c r="W3">
-        <v>0.1315354980737479</v>
+        <v>0.1172905525846702</v>
       </c>
       <c r="X3">
-        <v>0.1354779798136211</v>
+        <v>0.1352668946829672</v>
       </c>
       <c r="Y3">
-        <v>-0.003942481739873216</v>
+        <v>-0.01797634209829699</v>
       </c>
       <c r="Z3">
-        <v>0.05184668989547039</v>
+        <v>0.05964214711729623</v>
       </c>
       <c r="AA3">
-        <v>0.04292682926829269</v>
+        <v>0.04988252304355685</v>
       </c>
       <c r="AB3">
-        <v>0.1354779798136211</v>
+        <v>0.1352668946829672</v>
       </c>
       <c r="AC3">
-        <v>-0.09255115054532845</v>
+        <v>-0.08538437163941036</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -797,7 +797,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-4.65</v>
+        <v>-3.81</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -806,19 +806,19 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.03594897564746811</v>
+        <v>-0.0360488220266818</v>
       </c>
       <c r="AK3">
-        <v>-0.01506072874493927</v>
+        <v>-0.01602254089743051</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.62</v>
+        <v>-0.97</v>
       </c>
       <c r="AQ3">
-        <v>-24.83870967741936</v>
+        <v>-14.22680412371134</v>
       </c>
     </row>
   </sheetData>
